--- a/sources/ling_step5.xlsx
+++ b/sources/ling_step5.xlsx
@@ -417,27 +417,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R150"/>
+  <dimension ref="A1:S150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="280" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="280" customWidth="1" min="15" max="15"/>
     <col width="38" customWidth="1" min="16" max="16"/>
     <col width="38" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="38" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,12 +466,12 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -495,45 +496,50 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -560,22 +566,27 @@
           <t>10,20</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>874ba746-d7f5-4b19-9cf5-709a5bbb8de3</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>bb802c01-578a-4668-b589-3182cb1480f2</t>
         </is>
@@ -602,22 +613,27 @@
           <t>30</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>76accf4e-4c94-4698-aec5-96fe4410b827</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>cf24aa73-e196-4753-8f75-2a8677c4a59e</t>
         </is>
@@ -644,22 +660,27 @@
           <t>35</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>7b8461d8-84a3-466b-aaa6-9141b75dd3f5</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>01d44127-7e8b-46d0-8d3c-408e0dcf5438</t>
         </is>
@@ -686,32 +707,37 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>RDS</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Opponent can tap f,f to cancel the stagger after the throw and fall to the ground.; Special Team Tag Throw only with Jin,Heihachi,Panda or Kuma. Jin and Heihachi finish with a Stone head for a total damage of 30. Kuma and Panda finish with a Bear Hug for a total damage of 4,15.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>9736f1b9-bd3e-40b0-ace1-39836dcddbb5</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>c6fa184d-3605-4d0a-bc03-8bed3ee1e1a2</t>
         </is>
@@ -738,27 +764,32 @@
           <t>17,30</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Requires about a third screen distance.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>b9efd079-ac67-44e9-8ca8-ec04e15cac18</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>3403bf10-5918-4ca0-af7f-c089b6c78e82</t>
         </is>
@@ -790,27 +821,32 @@
           <t>Varies</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>99d4757d-183e-42be-b50c-3d5aeeb50259</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>be7d3077-c90b-42e5-939f-e8825a2ce1b0</t>
         </is>
@@ -837,27 +873,32 @@
           <t>Varies</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1_2</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -884,22 +925,27 @@
           <t>45</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -926,22 +972,27 @@
           <t>38</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -968,22 +1019,27 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1015,12 +1071,12 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -1045,45 +1101,50 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K15" s="1" t="inlineStr">
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="M15" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="N15" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="O15" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="P15" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr">
+      <c r="Q15" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q15" s="1" t="inlineStr">
+      <c r="R15" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R15" s="1" t="inlineStr">
+      <c r="S15" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1122,15 +1183,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>3d4e9688-0183-4bc6-a429-08ca94693a64</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>0ecdc0e5-882b-4668-ab00-82a75cb4b99a</t>
         </is>
@@ -1169,15 +1235,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>8faa3815-3232-42c4-9d9c-a12d27877788</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>c301e47b-3422-48f1-b63a-8545ec007e09</t>
         </is>
@@ -1216,15 +1287,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>674f6ed0-a19e-4d6e-9b1a-8f6ce8767295</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>e64a4f85-2e0c-473e-a18a-f687dd63e572</t>
         </is>
@@ -1263,15 +1339,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>f5249c34-48a5-44d5-88e5-b856cf2ac33f</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>b9b2e290-db35-4498-88bd-cf49fba834f0</t>
         </is>
@@ -1280,7 +1361,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F,1</t>
+          <t>f+1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1310,15 +1391,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>654c590b-31b1-4e48-a8c7-1490f53611b0</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>0576361d-32cb-4b30-8cff-8010fec75244</t>
         </is>
@@ -1327,7 +1413,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F,2</t>
+          <t>f+2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1357,15 +1443,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>326153e5-da5e-4e54-94cb-167f4e8438b9</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>05485f5b-c8d6-4703-b70d-a8cff30dcbed</t>
         </is>
@@ -1374,7 +1465,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F,3</t>
+          <t>f+3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1404,15 +1495,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>159ec1aa-69d1-4668-bcbe-997e418433fe</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>f3275c6c-946d-4f0b-bd70-6e480eca1fa9</t>
         </is>
@@ -1421,7 +1517,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F,4</t>
+          <t>f+4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1451,15 +1547,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>37b4723a-be31-4639-a5cd-059cf60d8091</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>aa40b9df-672f-4d85-ba90-ccdcc6b4063e</t>
         </is>
@@ -1498,15 +1599,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>b82887e9-a61d-4584-977d-ba57317e349d</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>a923518b-fe67-4965-bd42-d7ac2b636e3f</t>
         </is>
@@ -1545,15 +1651,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>bf84e8e5-f665-4138-bcb9-a26e3ef54bc7</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>5d332e14-a532-4cad-ad10-7cf71fc42b78</t>
         </is>
@@ -1592,15 +1703,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>38943d9f-55df-44bf-b43f-136c11d2677b</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>49bf1b20-3a34-418e-ab87-3f057c08f96a</t>
         </is>
@@ -1639,15 +1755,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>6abae15b-27f1-4104-8dfb-19656b0e4b80</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>5c77cfd5-db2e-486b-bf78-a5bfc930ec13</t>
         </is>
@@ -1656,7 +1777,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FC 1</t>
+          <t>FC+1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1686,15 +1807,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>69596f0f-8122-4867-a04d-918031b06b91</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>6e1dab43-d1a7-4938-93d9-418f8b9ac1e6</t>
         </is>
@@ -1703,7 +1829,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FC 2</t>
+          <t>FC+2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1733,15 +1859,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>1c16fcd8-3238-49f3-9cdc-29e5bdc5b9c3</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>d9a78570-4a7c-41a7-8221-23259ed7be12</t>
         </is>
@@ -1750,7 +1881,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FC 3</t>
+          <t>FC+3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1780,15 +1911,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>76e2df0e-a813-4660-908c-246d2b1d82fa</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>29b6b46f-815f-40fc-9351-8ef6498625c5</t>
         </is>
@@ -1797,7 +1933,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FC 4</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1827,15 +1963,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>518b7734-def4-4151-9778-6548a151545d</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>f1b2e14c-9234-44b9-b413-038443d1da0a</t>
         </is>
@@ -1844,7 +1985,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WS 1</t>
+          <t>WS+1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1874,15 +2015,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>5cdaf7f4-4a8b-4b30-b5c4-970f9f29a30d</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>58f45484-261f-4125-ab1b-f4704ca65a66</t>
         </is>
@@ -1891,7 +2037,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WS 2</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1921,15 +2067,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>493aab24-4dde-40c6-90c3-62c08b432bc3</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>a4b12e60-938d-4e77-8a5e-24c3f32a1e61</t>
         </is>
@@ -1938,7 +2089,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WS 3</t>
+          <t>WS+3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1968,15 +2119,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>7705f0ff-d1de-4875-a9f5-fcccd7e7d926</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>fe81c514-10df-452a-a6d6-d2807ee19444</t>
         </is>
@@ -1985,7 +2141,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WS 4</t>
+          <t>WS+4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2015,15 +2171,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>642e86ae-e1e5-4792-8202-8a35dc212a6c</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>ec1cda50-8fad-450c-bb74-3afe6a25812b</t>
         </is>
@@ -2062,15 +2223,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>13c8e9b0-e658-4dcc-967d-b7fa71d1effa</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>6e97e6f3-dbf1-4dde-a186-7cd7c3ddbfc5</t>
         </is>
@@ -2109,15 +2275,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>f9181a42-4111-43d9-bc55-9f4dcc0ff581</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>06a0142c-97ab-4a3e-9581-f40017c3a18b</t>
         </is>
@@ -2156,15 +2327,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>36e18bfa-d9b7-488f-924a-23d32baac0c5</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>88a32670-cb5c-4e71-b701-71c57d82b518</t>
         </is>
@@ -2203,15 +2379,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>9a35c142-35fa-42ef-9a4b-5d091de3ec50</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>ae7364bc-4c27-43f5-bda5-61c252199594</t>
         </is>
@@ -2243,12 +2424,12 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -2273,45 +2454,50 @@
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K42" s="1" t="inlineStr">
+      <c r="L42" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L42" s="1" t="inlineStr">
+      <c r="M42" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M42" s="1" t="inlineStr">
+      <c r="N42" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N42" s="1" t="inlineStr">
+      <c r="O42" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O42" s="1" t="inlineStr">
+      <c r="P42" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P42" s="1" t="inlineStr">
+      <c r="Q42" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q42" s="1" t="inlineStr">
+      <c r="R42" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R42" s="1" t="inlineStr">
+      <c r="S42" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -2355,15 +2541,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>0d5bcd50-3254-4d6f-b4c5-f468b127b2a3</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>4f39db8a-736d-4d36-b385-b0dddf727818</t>
         </is>
@@ -2407,15 +2598,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>18057ba1-27d5-432d-a37f-ce626c5d96df</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>6208d182-4079-4a5c-9189-6dec7615fd12</t>
         </is>
@@ -2464,15 +2660,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>a1386b61-24f6-4d3b-88d3-4e54daef5e51</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>08772236-a4a3-40c3-bbcd-893933eb996a</t>
         </is>
@@ -2516,15 +2717,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>7b3b5f6a-fb1c-4ac5-a4d7-a16b94eeed0c</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>a9f8dbb7-6556-4515-9072-e71b15fa96ba</t>
         </is>
@@ -2568,20 +2774,25 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Damage is 37 on a clean hit. On a counter hit Ling will do an automatic 1+3+4 taunt.</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>ada60b9c-5416-4a57-afff-308a55c3176b</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>e91952d3-8882-41ac-ab77-9b7c11730a3b</t>
         </is>
@@ -2630,15 +2841,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>872799b9-49ce-435c-b8ef-ea13476ed59c</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>ddbfb051-516e-4934-8f96-c810a5e3e832</t>
         </is>
@@ -2682,15 +2898,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>0a1984b5-fe08-48b1-9bec-e091c9ab2b74</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>12612140-1769-4c58-aac3-b351caf4ad7a</t>
         </is>
@@ -2744,20 +2965,25 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>Has to hit for Ling to go in RDS.</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>eb99dbf4-4081-4b01-9fbd-b152719bdd1d</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>cbf5c0d6-565b-492c-9e86-86f5e380a068</t>
         </is>
@@ -2806,15 +3032,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>1f252366-8668-4af0-b195-995f0ed7ed24</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>9166b9cd-c3c3-458a-aad8-799c49433c56</t>
         </is>
@@ -2858,20 +3089,25 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>mMM</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>a45a8361-3b4a-4e67-bc45-da8b314e5043</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>8bf0bc82-b4fe-4604-8c8c-aaef590ad31d</t>
         </is>
@@ -2920,15 +3156,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>mMM</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>eef6efe3-7a0b-4e48-8b25-1fdaf76cd199</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>bd70090f-b411-45ad-8797-1dc0d32ebf21</t>
         </is>
@@ -2955,12 +3196,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>4579fe1a-4ded-4ab1-8378-2eec09ff10b8</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>b99e421d-52d3-4689-b7d4-dbe0900af623</t>
         </is>
@@ -3004,20 +3250,25 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>RC GB</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>085e1996-b16b-4a63-a3d0-ae8152d065ea</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>c578a7b3-221f-4fe4-a117-dd1d49969717</t>
         </is>
@@ -3056,20 +3307,25 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>aadbdd07-dac3-4f6e-9230-207fed9671ef</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>20d0c7b5-efe5-4e46-86f0-179e7ba92fb6</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>085e1996-b16b-4a63-a3d0-ae8152d065ea</t>
         </is>
@@ -3108,20 +3364,25 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>1fe5e046-832f-40fb-bc3f-b47d5d1f9f82</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>61f591c1-a9cd-42fd-bc47-bb38e37d22e8</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>085e1996-b16b-4a63-a3d0-ae8152d065ea</t>
         </is>
@@ -3168,17 +3429,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>b929cc95-3142-4aba-8191-88bca5e84bf1</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>882e63b0-f559-4ef6-82b3-112a95589e60</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>085e1996-b16b-4a63-a3d0-ae8152d065ea</t>
         </is>
@@ -3222,25 +3488,30 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>BNc GB</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Bounce will occur only when the last hit is a counter hit.</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>d1404f6b-934d-4968-939b-d8bca00aa895</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>118c04cc-9a3e-4492-b06b-69c10b46a042</t>
         </is>
@@ -3284,20 +3555,25 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>CF KNDc</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>b0b13203-5198-40bb-af7c-078bdfeb8823</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>6a69aa0c-6e48-42b8-b188-a6084c11cfb9</t>
         </is>
@@ -3346,15 +3622,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>3a375440-f7c9-4294-9658-ce43e25f44a2</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>51f8c1c6-8fc6-4340-9572-9c8d0987ef71</t>
         </is>
@@ -3398,15 +3679,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>c230105d-5660-44a1-8e56-3200c351bcea</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>d87766ec-0585-4885-82e4-030adb204e93</t>
         </is>
@@ -3415,7 +3701,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WS 2 [~5]</t>
+          <t>WS+2 [~5]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3455,25 +3741,30 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>When a tag is buffered WS+2 will juggle on a regular hit.</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>d4d02dff-7fbd-421d-8cc8-c8fe331eee39</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>5ba12b9a-3d74-4e93-ba59-097c6a0a01d4</t>
         </is>
@@ -3482,7 +3773,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WS 2~F</t>
+          <t>WS+2~F</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3517,20 +3808,25 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>3e13f208-6740-4bd0-b40f-cb937d7c837a</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>9f11293a-e276-4d5d-a06e-42bfb2cfbbb2</t>
         </is>
@@ -3574,20 +3870,25 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>321a983c-005f-47c0-aae9-9e92eb3084a6</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>0b85571b-13f9-40dd-b439-05dd5d183abe</t>
         </is>
@@ -3596,7 +3897,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FC,DF+2</t>
+          <t>FC+DF+2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3636,15 +3937,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>c86a461d-9853-409e-8dbf-c140f78957bc</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>29fe6146-6448-4dc1-b260-e1da0f2682fb</t>
         </is>
@@ -3653,7 +3959,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FC,df+2,1</t>
+          <t>FC+df+2,1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3688,20 +3994,25 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>ll</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>a2d0c94a-e4f1-4b84-867d-a8aacd632dde</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>71535751-0aff-41bc-b353-d8de0f10a87c</t>
         </is>
@@ -3745,20 +4056,25 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>6ca8b195-fd70-49e9-95ff-f068baffeef4</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>5dd79b04-bd05-487e-b258-4b23cbf1948f</t>
         </is>
@@ -3802,15 +4118,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>a87e6188-7f43-46a4-ab07-74e7a6df6d75</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>62fb2034-0e33-454a-9879-4446c986e9d7</t>
         </is>
@@ -3854,15 +4175,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>ba40070f-3541-4774-b6c2-3e6514a34549</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>2f59aa03-4e29-4e9e-9560-3826ac149e32</t>
         </is>
@@ -3906,20 +4232,25 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>!</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>c7ad3516-8d27-4ca8-b1c6-c74ee15c88c8</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>cf476e8d-471d-4590-b67d-27468570b504</t>
         </is>
@@ -3968,15 +4299,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>c01958d7-8362-449b-af6c-027346aabe6a</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>58a60921-36a8-4076-a001-e02f71d9264c</t>
         </is>
@@ -4020,20 +4356,25 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>Lhhm</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>fcaee446-6310-493e-a29b-7980137a4e3d</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>32c666d4-5778-4d06-865d-1e3dba39b4b0</t>
         </is>
@@ -4065,12 +4406,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t>d09dd708-e5fd-49ca-921c-de3f19c95bdb</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>b426aeb9-b274-476a-ba58-d34a83e4bd86</t>
         </is>
@@ -4097,17 +4443,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
         <is>
           <t>Depending on your opponents position before the move Ling can end up in RDS.</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>fb27b361-92bd-42ac-894f-527ba7204cc5</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>7bb439b3-adaf-442e-9b88-4eb1bdc6c4e8</t>
         </is>
@@ -4151,20 +4502,25 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>Depending on your opponents position before the move Ling can end up in RDS.</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>75cb1604-b604-46ef-8091-2243270682f9</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>5a8a5d0a-e454-47f0-a5e5-2039447cd13b</t>
         </is>
@@ -4208,15 +4564,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>c7ccb049-feaa-4dbb-960b-d898c19e8cc7</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>cca3e22f-9227-4dfe-b4fa-d24c56031928</t>
         </is>
@@ -4260,20 +4621,25 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>KS SLDc</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>4f70efc9-f29d-499b-9b59-0bfcb8aec97b</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>2980281e-5707-48f4-b8e4-563db7ddb16e</t>
         </is>
@@ -4317,15 +4683,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>059b4353-a8cd-44d2-b4e7-239c136e63c4</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>6908745c-786b-41a4-960f-f5f3f0ee5d05</t>
         </is>
@@ -4334,7 +4705,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WS 4</t>
+          <t>WS+4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4369,15 +4740,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>77e41785-f559-4e94-935a-f393bfbd4411</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>83f5e942-21b7-4034-b5cc-72dabb3f9bb5</t>
         </is>
@@ -4421,20 +4797,25 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>dd5f73a9-6cab-4ba4-91a2-5bba6df2ac16</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>113a7f27-ae61-41a3-9373-36866580e20f</t>
         </is>
@@ -4443,7 +4824,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FC,df+4</t>
+          <t>FC+df+4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4463,15 +4844,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>d288a6b0-c084-494a-b866-6808c8f0b42b</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>b3d5cc22-7a23-424a-a6a0-ee5e8a86234a</t>
         </is>
@@ -4480,7 +4866,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FC,df+4,4</t>
+          <t>FC+df+4,4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4515,20 +4901,25 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>980d698e-01ea-48fb-b9e2-41fd6d42b795</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>c4d103c1-775e-4596-b5a2-58bbf692c078</t>
         </is>
@@ -4537,7 +4928,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SS 4 [~B]</t>
+          <t>SS+4 [~B]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4582,15 +4973,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>hh</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>575f73c7-dbfa-4d31-8a40-4db2663c3a4d</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>66a76604-e344-4e65-8239-d0cabdc1a81f</t>
         </is>
@@ -4617,12 +5013,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>ce011a94-5f40-4d47-8059-3a12141afc50</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>a4ae5fdb-c240-4fff-ba78-84ecd64e87b0</t>
         </is>
@@ -4666,25 +5067,30 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>Damage increases to 30 then 35 as you Hypnotist Walk longer. Clean Hit damage will be 37,45 or 52.</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>4fb4d6e5-1428-47b8-84f7-b084a82d6f57</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>6c08bafe-f024-4808-b991-d6e90f7678ab</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="R86" t="inlineStr">
         <is>
           <t>ce011a94-5f40-4d47-8059-3a12141afc50</t>
         </is>
@@ -4711,17 +5117,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>cde3cbb6-39e4-4bbd-8d1e-59d63f6766a9</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>97d5cd5d-2c92-4e6f-9259-be9897218dd1</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>ce011a94-5f40-4d47-8059-3a12141afc50</t>
         </is>
@@ -4730,7 +5141,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FC,db+3+4</t>
+          <t>FC+db+3+4</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4753,12 +5164,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
         <is>
           <t>9cd78cfe-f850-44ec-8cbc-c1744ce20f54</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>9c49960f-f109-49bd-931b-0ac227f9a527</t>
         </is>
@@ -4790,12 +5206,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
         <is>
           <t>3f6ba135-24e6-44ae-89c1-09dbdf045c6a</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>666f30a5-68a7-46f5-9686-5bf86fc4681e</t>
         </is>
@@ -4827,12 +5248,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
         <is>
           <t>def84375-5011-4b11-84a0-885a34b25d85</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>c05e0674-0400-4165-9779-3e1a957236ba</t>
         </is>
@@ -4859,12 +5285,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t>55f10e0e-b8fe-4478-8d4c-2fe839b19882</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>0f9d5da1-c35e-4d47-a0e5-ab212de8decf</t>
         </is>
@@ -4891,12 +5322,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
         <is>
           <t>0f3dc3b0-1a09-42da-8a39-ca793941d837</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>1a5f0a2d-10a3-497b-9fcd-29520e5d3b81</t>
         </is>
@@ -4928,12 +5364,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
         <is>
           <t>66d0bc20-2aec-47e1-a748-5b027c60d425</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>ce17d917-2b59-4a46-b0e4-7550d494f83a</t>
         </is>
@@ -4957,15 +5398,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>4f00b275-65c1-4e31-9c5b-02f3961f09dc</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>b4faf1a5-69a3-42f4-aedb-dbec07df51de</t>
         </is>
@@ -5012,12 +5458,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
         <is>
           <t>0a724735-c333-4d7c-9b41-4bda114587c0</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>18706352-d2c1-4871-9334-8733a8ca4c58</t>
         </is>
@@ -5049,12 +5500,12 @@
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
@@ -5079,45 +5530,50 @@
       </c>
       <c r="J98" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K98" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K98" s="1" t="inlineStr">
+      <c r="L98" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L98" s="1" t="inlineStr">
+      <c r="M98" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M98" s="1" t="inlineStr">
+      <c r="N98" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N98" s="1" t="inlineStr">
+      <c r="O98" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O98" s="1" t="inlineStr">
+      <c r="P98" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P98" s="1" t="inlineStr">
+      <c r="Q98" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q98" s="1" t="inlineStr">
+      <c r="R98" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R98" s="1" t="inlineStr">
+      <c r="S98" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -5129,12 +5585,12 @@
           <t>Moves starting from Rain Dance Stance only - RDS</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>1463bdfa-6bdd-49d2-a3ac-280786b102dd</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>e386e57a-42fe-4297-8e0a-8db74be4ac98</t>
         </is>
@@ -5166,12 +5622,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
         <is>
           <t>e90f1b2c-7bb0-4304-acf8-33dbc4a1634a</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>fa074052-d35d-4fa9-a46b-d4ad62900392</t>
         </is>
@@ -5200,15 +5661,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>40a1fbca-708f-4ab1-be5c-c60615ba0680</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>30e4a770-a0c0-4eda-b753-55a3bb608e8b</t>
         </is>
@@ -5252,25 +5718,30 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t>hhm</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>All hits are guaranteed if the first hit is a counter hit.</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>9629caf3-6f10-4e33-a2d4-d73deedf7469</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>f6a9b652-ae23-4cef-8ee9-a3d3598a2405</t>
         </is>
@@ -5319,15 +5790,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>ba040e65-ad5e-4c64-a392-d40def463053</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>a0fb96a0-a340-4e63-9779-5fd48da4a1d8</t>
         </is>
@@ -5376,20 +5852,25 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>FCDc</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>fbbbf1af-b438-4a15-91dd-a6c778a458e0</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>13025283-ecef-4950-b35f-93ace7ce4239</t>
         </is>
@@ -5433,20 +5914,25 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t>FCDc</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>1d476db7-0fef-4df3-a76a-9ebc7782df53</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>8a7c66bd-7aff-447b-bf87-05c78692484b</t>
         </is>
@@ -5490,15 +5976,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr">
+      <c r="P106" t="inlineStr">
         <is>
           <t>5936552e-0d20-43e9-a341-81e555eede34</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>625a8401-986c-4710-94eb-d3e72202ab8e</t>
         </is>
@@ -5530,12 +6021,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
         <is>
           <t>83d45d20-abe6-4ff5-bd03-2cf9f2d0b03d</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
+      <c r="Q107" t="inlineStr">
         <is>
           <t>9af711df-7250-47e6-8b78-57bcd1416cab</t>
         </is>
@@ -5567,12 +6063,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
         <is>
           <t>72ceb8fa-8c13-414e-abde-e93840b782c9</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
+      <c r="Q108" t="inlineStr">
         <is>
           <t>bd8643e7-8f94-455b-8c84-3e50e022e63e</t>
         </is>
@@ -5604,12 +6105,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
         <is>
           <t>228070f6-c47f-4f7b-a6b0-76d8abe818f3</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
+      <c r="Q109" t="inlineStr">
         <is>
           <t>453a6061-7c9d-4d99-a5a9-8b963c8c846d</t>
         </is>
@@ -5658,25 +6164,30 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="N110" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
+      <c r="P110" t="inlineStr">
         <is>
           <t>c6902a2f-fe58-4489-baf6-20e02a7ecb01</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>c79e62a9-b2b5-417d-a013-a0dbefa5bfd4</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr">
+      <c r="R110" t="inlineStr">
         <is>
           <t>228070f6-c47f-4f7b-a6b0-76d8abe818f3</t>
         </is>
@@ -5700,20 +6211,25 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t>!</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="N111" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr">
+      <c r="P111" t="inlineStr">
         <is>
           <t>cc68a12e-0e8a-42a9-bfd6-5f7c9687cf3f</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>6053fba2-dfd8-4f56-b15b-a3c1c488ecc0</t>
         </is>
@@ -5757,25 +6273,30 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr">
+      <c r="N112" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr">
+      <c r="O112" t="inlineStr">
         <is>
           <t>Will not JG when hitting opponent from the back unless it's a counter hit.</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
+      <c r="P112" t="inlineStr">
         <is>
           <t>24ef26f6-00ec-47ed-889c-69992f4e72c7</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
+      <c r="Q112" t="inlineStr">
         <is>
           <t>5ebba108-f22a-4c3b-a3ec-6d5a528427b3</t>
         </is>
@@ -5807,12 +6328,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
         <is>
           <t>07193dd0-f923-4b9e-bcdf-cfe43c6d0073</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
+      <c r="Q113" t="inlineStr">
         <is>
           <t>e5b6da5d-b3af-4179-8d6b-8e6204f756df</t>
         </is>
@@ -5844,12 +6370,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
         <is>
           <t>087533d3-7b32-4028-9903-882f53af94af</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
+      <c r="Q114" t="inlineStr">
         <is>
           <t>e1e4f79f-e3d1-46f5-b04d-4ffffd718e39</t>
         </is>
@@ -5881,12 +6412,12 @@
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
@@ -5911,45 +6442,50 @@
       </c>
       <c r="J117" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K117" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K117" s="1" t="inlineStr">
+      <c r="L117" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L117" s="1" t="inlineStr">
+      <c r="M117" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M117" s="1" t="inlineStr">
+      <c r="N117" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N117" s="1" t="inlineStr">
+      <c r="O117" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O117" s="1" t="inlineStr">
+      <c r="P117" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P117" s="1" t="inlineStr">
+      <c r="Q117" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q117" s="1" t="inlineStr">
+      <c r="R117" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R117" s="1" t="inlineStr">
+      <c r="S117" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -5961,12 +6497,12 @@
           <t>Moves starting from Art of Phoenix only - AOP</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr">
+      <c r="P118" t="inlineStr">
         <is>
           <t>d0d46428-c4a7-4d18-9f37-5ea60725fffe</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr">
+      <c r="Q118" t="inlineStr">
         <is>
           <t>0234698e-52aa-498c-b2c4-ef87fa8dc9ef</t>
         </is>
@@ -5993,12 +6529,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
         <is>
           <t>8b15273f-5f2b-4cdd-b372-a139740596d7</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
+      <c r="Q119" t="inlineStr">
         <is>
           <t>34f4bdbd-103e-4046-ba2a-bd5980a57e52</t>
         </is>
@@ -6042,20 +6583,25 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr">
+      <c r="N120" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr">
+      <c r="P120" t="inlineStr">
         <is>
           <t>003c8781-29d8-4d26-bf44-4e2cefd2c2da</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
+      <c r="Q120" t="inlineStr">
         <is>
           <t>cda84b7f-2644-4827-aa86-f03b254f7851</t>
         </is>
@@ -6099,15 +6645,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr">
+      <c r="P121" t="inlineStr">
         <is>
           <t>1beba94c-235e-4b33-a3d1-b33d99c0793d</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
+      <c r="Q121" t="inlineStr">
         <is>
           <t>be6a3968-d8f0-4a1a-b370-c35a107e1fc0</t>
         </is>
@@ -6151,20 +6702,25 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr">
+      <c r="N122" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
+      <c r="P122" t="inlineStr">
         <is>
           <t>b29ebb4f-71c3-46ff-a564-c0665f8ce29a</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
+      <c r="Q122" t="inlineStr">
         <is>
           <t>411036bf-7019-4530-86c9-9e8210bb915a</t>
         </is>
@@ -6208,20 +6764,25 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="N123" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
+      <c r="P123" t="inlineStr">
         <is>
           <t>8e78110f-4b67-4ae2-b09e-28d0f56ba1af</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr">
+      <c r="Q123" t="inlineStr">
         <is>
           <t>f8f8275e-9d8a-4076-a6c8-038a0fdaf8fb</t>
         </is>
@@ -6265,20 +6826,25 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
+      <c r="N124" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
+      <c r="P124" t="inlineStr">
         <is>
           <t>3a25fb5f-d393-470f-b5d2-7c493209f04b</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
+      <c r="Q124" t="inlineStr">
         <is>
           <t>7c126533-6eef-48ee-9863-c4730809a72a</t>
         </is>
@@ -6310,12 +6876,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
         <is>
           <t>c5b8ea02-4707-499c-be21-67ea8611cd84</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr">
+      <c r="Q125" t="inlineStr">
         <is>
           <t>a9b6f321-685b-4561-b08e-60109cd7cf45</t>
         </is>
@@ -6364,15 +6935,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr">
+      <c r="P126" t="inlineStr">
         <is>
           <t>474c2981-1853-4472-ac5b-4f84dcabe5cb</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr">
+      <c r="Q126" t="inlineStr">
         <is>
           <t>735ac30b-4005-4ec2-ba93-899bfa69dce6</t>
         </is>
@@ -6401,20 +6977,25 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
+      <c r="N127" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
+      <c r="P127" t="inlineStr">
         <is>
           <t>580488b1-c279-4f84-8bd0-54174c845400</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr">
+      <c r="Q127" t="inlineStr">
         <is>
           <t>93efb4e9-751c-41ba-9b75-1a89423ae246</t>
         </is>
@@ -6463,15 +7044,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t>mh</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
+      <c r="P128" t="inlineStr">
         <is>
           <t>434d7516-7ca3-4d2b-a419-c5707d1259cb</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
+      <c r="Q128" t="inlineStr">
         <is>
           <t>ebbaa062-52f7-4b7a-b7a6-1d78260b9385</t>
         </is>
@@ -6520,15 +7106,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr">
+      <c r="P129" t="inlineStr">
         <is>
           <t>062c9f96-61a5-4f97-bdb3-64ab4c85395a</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr">
+      <c r="Q129" t="inlineStr">
         <is>
           <t>25e847da-7d68-4b0d-9121-e5320dded288</t>
         </is>
@@ -6577,20 +7168,25 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr">
+      <c r="N130" t="inlineStr">
         <is>
           <t>JG RC</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr">
+      <c r="P130" t="inlineStr">
         <is>
           <t>b9ac8d5c-3cf5-47f5-b133-0e9dbc800ab0</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr">
+      <c r="Q130" t="inlineStr">
         <is>
           <t>671b59e4-956d-4b68-b2da-29229743c199</t>
         </is>
@@ -6639,20 +7235,25 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr">
+      <c r="N131" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr">
+      <c r="P131" t="inlineStr">
         <is>
           <t>360f8c33-8f4c-472d-b48b-afb45aa2824a</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr">
+      <c r="Q131" t="inlineStr">
         <is>
           <t>5eb1e44b-2bc2-4127-9f20-8729e9de6e3f</t>
         </is>
@@ -6679,12 +7280,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr">
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
         <is>
           <t>987a1676-d0c0-438a-8e69-8ce9ec35af7f</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr">
+      <c r="Q132" t="inlineStr">
         <is>
           <t>5c053e58-fff3-49f3-a06a-8605548e8675</t>
         </is>
@@ -6728,15 +7334,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O133" t="inlineStr">
+      <c r="P133" t="inlineStr">
         <is>
           <t>fea0d91f-39e3-4926-a9ed-3bc833370e79</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr">
+      <c r="Q133" t="inlineStr">
         <is>
           <t>26a956ee-8ce8-41f0-baad-ab1a0c615698</t>
         </is>
@@ -6775,15 +7386,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="O134" t="inlineStr">
+      <c r="P134" t="inlineStr">
         <is>
           <t>eba52a6a-4354-422e-bcd5-c23c11453761</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr">
+      <c r="Q134" t="inlineStr">
         <is>
           <t>a21db126-2f0b-44b8-ab96-9549740a1cad</t>
         </is>
@@ -6812,15 +7428,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="O135" t="inlineStr">
+      <c r="P135" t="inlineStr">
         <is>
           <t>e8b6d600-c44b-4d97-a4b9-6d2ed3d201a9</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr">
+      <c r="Q135" t="inlineStr">
         <is>
           <t>79da43f9-f15c-401c-be49-caf21a5e722f</t>
         </is>
@@ -6864,20 +7485,25 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
+      <c r="N136" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr">
+      <c r="P136" t="inlineStr">
         <is>
           <t>c38c4db9-3d0c-46ec-91af-0cd4508ee5cd</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr">
+      <c r="Q136" t="inlineStr">
         <is>
           <t>aa27bb14-ccf7-47c5-aa90-dcf490be8022</t>
         </is>
@@ -6926,15 +7552,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O137" t="inlineStr">
+      <c r="P137" t="inlineStr">
         <is>
           <t>8fa918ec-1f5e-4f20-8e03-75328b81eaf2</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr">
+      <c r="Q137" t="inlineStr">
         <is>
           <t>cb4812ee-6be2-484c-9112-114329bbd26d</t>
         </is>
@@ -6983,15 +7614,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O138" t="inlineStr">
+      <c r="P138" t="inlineStr">
         <is>
           <t>2a342267-1fd0-44f8-8e57-187e4ece4da1</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr">
+      <c r="Q138" t="inlineStr">
         <is>
           <t>b0b147bc-05ce-41c1-8fd6-987028a6dfb4</t>
         </is>
@@ -7035,25 +7671,30 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t>mmmm</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr">
+      <c r="N139" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr">
+      <c r="O139" t="inlineStr">
         <is>
           <t>Input d+1+2 after the first kick to put ling back into AOP.</t>
         </is>
       </c>
-      <c r="O139" t="inlineStr">
+      <c r="P139" t="inlineStr">
         <is>
           <t>4016de06-dd0b-4e13-a819-95c550e4176c</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr">
+      <c r="Q139" t="inlineStr">
         <is>
           <t>529abc67-6bea-4927-9113-dabede12c8af</t>
         </is>
@@ -7102,15 +7743,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr">
+      <c r="P140" t="inlineStr">
         <is>
           <t>9023ae52-908d-4bd7-8658-dbf302ba9bac</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr">
+      <c r="Q140" t="inlineStr">
         <is>
           <t>5a5ef6ea-0bcb-47b5-8754-1fb0fa1ef756</t>
         </is>
@@ -7142,12 +7788,12 @@
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
@@ -7172,45 +7818,50 @@
       </c>
       <c r="J143" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K143" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K143" s="1" t="inlineStr">
+      <c r="L143" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L143" s="1" t="inlineStr">
+      <c r="M143" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M143" s="1" t="inlineStr">
+      <c r="N143" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N143" s="1" t="inlineStr">
+      <c r="O143" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O143" s="1" t="inlineStr">
+      <c r="P143" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P143" s="1" t="inlineStr">
+      <c r="Q143" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q143" s="1" t="inlineStr">
+      <c r="R143" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R143" s="1" t="inlineStr">
+      <c r="S143" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7249,20 +7900,25 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t>[!]</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr">
+      <c r="O144" t="inlineStr">
         <is>
           <t>Damage increases to 50 then 80 as you Hypnotist Walk longer.</t>
         </is>
       </c>
-      <c r="O144" t="inlineStr">
+      <c r="P144" t="inlineStr">
         <is>
           <t>25f9b418-8f7d-4dca-b2a8-04c676fbd4aa</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr">
+      <c r="Q144" t="inlineStr">
         <is>
           <t>d3a225ab-b800-42d6-9487-98fb5a037e09</t>
         </is>
@@ -7294,17 +7950,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O145" t="inlineStr">
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
         <is>
           <t>26909f52-7512-44a5-9bc0-0b5669dd6609</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr">
+      <c r="Q145" t="inlineStr">
         <is>
           <t>ee40cdb8-7235-4abd-89c4-ab82725d3223</t>
         </is>
       </c>
-      <c r="Q145" t="inlineStr">
+      <c r="R145" t="inlineStr">
         <is>
           <t>25f9b418-8f7d-4dca-b2a8-04c676fbd4aa</t>
         </is>
@@ -7336,12 +7997,12 @@
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
@@ -7366,45 +8027,50 @@
       </c>
       <c r="J148" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K148" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K148" s="1" t="inlineStr">
+      <c r="L148" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L148" s="1" t="inlineStr">
+      <c r="M148" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M148" s="1" t="inlineStr">
+      <c r="N148" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N148" s="1" t="inlineStr">
+      <c r="O148" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O148" s="1" t="inlineStr">
+      <c r="P148" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P148" s="1" t="inlineStr">
+      <c r="Q148" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q148" s="1" t="inlineStr">
+      <c r="R148" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R148" s="1" t="inlineStr">
+      <c r="S148" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7423,15 +8089,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t>mhhmmMLLmm</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr">
+      <c r="Q149" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr">
+      <c r="S149" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -7450,15 +8121,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t>mhhLLmmllmm</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr">
+      <c r="Q150" t="inlineStr">
         <is>
           <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr">
+      <c r="S150" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/ling_step5.xlsx
+++ b/sources/ling_step5.xlsx
@@ -893,6 +893,11 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
@@ -940,6 +945,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
@@ -987,6 +997,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
@@ -1032,6 +1047,11 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -8097,6 +8117,11 @@
           <t>mhhmmMLLmm</t>
         </is>
       </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
+        </is>
+      </c>
       <c r="Q149" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
@@ -8127,6 +8152,11 @@
       <c r="K150" t="inlineStr">
         <is>
           <t>mhhLLmmllmm</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
